--- a/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0003T0006Z000C1N75_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0003T0006Z000C1N75_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>67.79503712173577</v>
+        <v>11.01669353228206</v>
       </c>
       <c r="D2" t="n">
-        <v>68.68004551938654</v>
+        <v>11.16050739690031</v>
       </c>
       <c r="E2" t="n">
-        <v>15.60941135299524</v>
+        <v>2.536529344861727</v>
       </c>
       <c r="F2" t="n">
-        <v>15.91426545605835</v>
+        <v>2.586068136609481</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>61.20924171953369</v>
+        <v>9.946501779424226</v>
       </c>
       <c r="D3" t="n">
-        <v>62.00693420215885</v>
+        <v>10.07612680785081</v>
       </c>
       <c r="E3" t="n">
-        <v>15.60941135299524</v>
+        <v>2.536529344861727</v>
       </c>
       <c r="F3" t="n">
-        <v>15.91426545605835</v>
+        <v>2.586068136609481</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>53.28812900591983</v>
+        <v>8.659320963461974</v>
       </c>
       <c r="D4" t="n">
-        <v>54.01006799569393</v>
+        <v>8.776636049300263</v>
       </c>
       <c r="E4" t="n">
-        <v>15.60941135299524</v>
+        <v>2.536529344861727</v>
       </c>
       <c r="F4" t="n">
-        <v>15.91426545605835</v>
+        <v>2.586068136609481</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>46.53581825468279</v>
+        <v>7.562070466385954</v>
       </c>
       <c r="D5" t="n">
-        <v>47.17302813705556</v>
+        <v>7.665617072271528</v>
       </c>
       <c r="E5" t="n">
-        <v>15.60941135299524</v>
+        <v>2.536529344861727</v>
       </c>
       <c r="F5" t="n">
-        <v>15.91426545605835</v>
+        <v>2.586068136609481</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>28.54575356125149</v>
+        <v>4.638684953703367</v>
       </c>
       <c r="D6" t="n">
-        <v>28.46668096321837</v>
+        <v>4.625835656522985</v>
       </c>
       <c r="E6" t="n">
-        <v>15.60941135299524</v>
+        <v>2.536529344861727</v>
       </c>
       <c r="F6" t="n">
-        <v>15.91426545605835</v>
+        <v>2.586068136609481</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>31.1798147011012</v>
+        <v>5.066719888928946</v>
       </c>
       <c r="D7" t="n">
-        <v>31.77420930051421</v>
+        <v>5.163309011333559</v>
       </c>
       <c r="E7" t="n">
-        <v>15.60941135299524</v>
+        <v>2.536529344861727</v>
       </c>
       <c r="F7" t="n">
-        <v>15.91426545605835</v>
+        <v>2.586068136609481</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>18.38402371823122</v>
+        <v>2.987403854212574</v>
       </c>
       <c r="D8" t="n">
-        <v>18.78789813654322</v>
+        <v>3.053033447188274</v>
       </c>
       <c r="E8" t="n">
-        <v>15.60941135299524</v>
+        <v>2.536529344861727</v>
       </c>
       <c r="F8" t="n">
-        <v>15.91426545605835</v>
+        <v>2.586068136609481</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>26.81920611043808</v>
+        <v>4.358120992946189</v>
       </c>
       <c r="D9" t="n">
-        <v>25.98137020516872</v>
+        <v>4.221972658339917</v>
       </c>
       <c r="E9" t="n">
-        <v>15.60941135299524</v>
+        <v>2.536529344861727</v>
       </c>
       <c r="F9" t="n">
-        <v>15.91426545605835</v>
+        <v>2.586068136609481</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>24.33737948991562</v>
+        <v>3.954824167111288</v>
       </c>
       <c r="D10" t="n">
-        <v>23.44127084958713</v>
+        <v>3.809206513057909</v>
       </c>
       <c r="E10" t="n">
-        <v>15.60941135299524</v>
+        <v>2.536529344861727</v>
       </c>
       <c r="F10" t="n">
-        <v>15.91426545605835</v>
+        <v>2.586068136609481</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>20.50582757448632</v>
+        <v>3.332196980854027</v>
       </c>
       <c r="D11" t="n">
-        <v>19.6582512580528</v>
+        <v>3.19446582943358</v>
       </c>
       <c r="E11" t="n">
-        <v>15.60941135299524</v>
+        <v>2.536529344861727</v>
       </c>
       <c r="F11" t="n">
-        <v>15.91426545605835</v>
+        <v>2.586068136609481</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>34.7481803658553</v>
+        <v>5.646579309451488</v>
       </c>
       <c r="D12" t="n">
-        <v>33.84874597649468</v>
+        <v>5.500421221180386</v>
       </c>
       <c r="E12" t="n">
-        <v>15.60941135299524</v>
+        <v>2.536529344861727</v>
       </c>
       <c r="F12" t="n">
-        <v>15.91426545605835</v>
+        <v>2.586068136609481</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>41.63673220804377</v>
+        <v>6.765968983807112</v>
       </c>
       <c r="D13" t="n">
-        <v>40.85624624926597</v>
+        <v>6.639140015505721</v>
       </c>
       <c r="E13" t="n">
-        <v>15.60941135299524</v>
+        <v>2.536529344861727</v>
       </c>
       <c r="F13" t="n">
-        <v>15.91426545605835</v>
+        <v>2.586068136609481</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>52.9593420608492</v>
+        <v>8.605893084887995</v>
       </c>
       <c r="D14" t="n">
-        <v>52.06150625562954</v>
+        <v>8.459994766539801</v>
       </c>
       <c r="E14" t="n">
-        <v>15.60941135299524</v>
+        <v>2.536529344861727</v>
       </c>
       <c r="F14" t="n">
-        <v>15.91426545605835</v>
+        <v>2.586068136609481</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>57.259031524397</v>
+        <v>9.304592622714512</v>
       </c>
       <c r="D15" t="n">
-        <v>56.51310225163922</v>
+        <v>9.183379115891375</v>
       </c>
       <c r="E15" t="n">
-        <v>15.60941135299524</v>
+        <v>2.536529344861727</v>
       </c>
       <c r="F15" t="n">
-        <v>15.91426545605835</v>
+        <v>2.586068136609481</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
